--- a/Result/profitability/2376.xlsx
+++ b/Result/profitability/2376.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>4.297499999999999</v>
+        <v>5.16625</v>
       </c>
       <c r="N2" t="n">
-        <v>11.52625</v>
+        <v>11.44375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>3.98125</v>
+        <v>4.66125</v>
       </c>
       <c r="N3" t="n">
-        <v>11.97875</v>
+        <v>11.91625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>3.47</v>
+        <v>4.12125</v>
       </c>
       <c r="N4" t="n">
-        <v>12.61625</v>
+        <v>12.20625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>2.89125</v>
+        <v>3.555</v>
       </c>
       <c r="N5" t="n">
-        <v>12.8975</v>
+        <v>12.9225</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>2.40875</v>
+        <v>3.07125</v>
       </c>
       <c r="N6" t="n">
-        <v>14.06125</v>
+        <v>14.025</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8975</v>
+        <v>2.57625</v>
       </c>
       <c r="N7" t="n">
-        <v>15.0525</v>
+        <v>14.97</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>1.49875</v>
+        <v>1.74875</v>
       </c>
       <c r="N8" t="n">
-        <v>16.225</v>
+        <v>15.92625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>144214</v>
+      </c>
+      <c r="D75" t="n">
+        <v>130341</v>
+      </c>
+      <c r="E75" t="n">
+        <v>13873</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8120</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1330</v>
+      </c>
+      <c r="J75" t="n">
+        <v>9451</v>
+      </c>
+      <c r="K75" t="n">
+        <v>6606</v>
+      </c>
+      <c r="L75" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="M75" t="n">
+        <v>5.404999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10.5675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2544529262086512</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.390000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1990008326394671</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.167032967032967</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02123142250530785</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
